--- a/Res_ConvLSTM/DroughtDataset_model_testing_1753806888_individual_h_9.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1753806888_individual_h_9.xlsx
@@ -658,7 +658,7 @@
         <v>0.008510362272481009</v>
       </c>
       <c r="C2" t="n">
-        <v>56816802</v>
+        <v>6312978</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>56816802</v>
+        <v>6312978</v>
       </c>
       <c r="K2" t="n">
-        <v>39628396</v>
+        <v>3936520</v>
       </c>
       <c r="L2" t="n">
-        <v>21583038</v>
+        <v>1871352</v>
       </c>
       <c r="M2" t="n">
-        <v>5109164</v>
+        <v>399075</v>
       </c>
       <c r="N2" t="n">
-        <v>152366</v>
+        <v>9647</v>
       </c>
       <c r="O2" t="n">
-        <v>3109877</v>
+        <v>256782</v>
       </c>
       <c r="P2" t="n">
-        <v>1103527</v>
+        <v>95420</v>
       </c>
       <c r="Q2" t="n">
         <v>0.9999390244483948</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8554545044898987</v>
+        <v>0.7636198997497559</v>
       </c>
       <c r="S2" t="n">
-        <v>0.73023521900177</v>
+        <v>0.5708780884742737</v>
       </c>
       <c r="T2" t="n">
-        <v>0.658588707447052</v>
+        <v>0.4622229933738708</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2290914952754974</v>
+        <v>0.1325829476118088</v>
       </c>
       <c r="V2" t="n">
-        <v>0.6930518746376038</v>
+        <v>0.5158108472824097</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8141574859619141</v>
+        <v>0.6396771669387817</v>
       </c>
       <c r="X2" t="n">
-        <v>56816802</v>
+        <v>6312978</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>56816802</v>
+        <v>6312978</v>
       </c>
       <c r="AF2" t="n">
-        <v>43199395</v>
+        <v>4763805</v>
       </c>
       <c r="AG2" t="n">
-        <v>26831006</v>
+        <v>3006353</v>
       </c>
       <c r="AH2" t="n">
-        <v>7210544</v>
+        <v>805109</v>
       </c>
       <c r="AI2" t="n">
-        <v>531451</v>
+        <v>59219</v>
       </c>
       <c r="AJ2" t="n">
-        <v>4136352</v>
+        <v>460827</v>
       </c>
       <c r="AK2" t="n">
-        <v>1621076</v>
+        <v>180323</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9560797214508057</v>
+        <v>0.9549221992492676</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9115321636199951</v>
+        <v>0.912146270275116</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8582335114479065</v>
+        <v>0.8583800792694092</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6618483662605286</v>
+        <v>0.6608968377113342</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9020155668258667</v>
+        <v>0.9020029902458191</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314467906951904</v>
+        <v>0.9314685463905334</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.002038439189791413</v>
       </c>
       <c r="C3" t="n">
-        <v>3259</v>
+        <v>363</v>
       </c>
       <c r="D3" t="n">
-        <v>39628396</v>
+        <v>3936520</v>
       </c>
       <c r="E3" t="n">
-        <v>5312497</v>
+        <v>984894</v>
       </c>
       <c r="F3" t="n">
-        <v>149131</v>
+        <v>46296</v>
       </c>
       <c r="G3" t="n">
-        <v>9949</v>
+        <v>2820</v>
       </c>
       <c r="H3" t="n">
-        <v>11881</v>
+        <v>4473</v>
       </c>
       <c r="I3" t="n">
-        <v>515</v>
+        <v>289</v>
       </c>
       <c r="J3" t="n">
-        <v>90146133</v>
+        <v>10016237</v>
       </c>
       <c r="K3" t="n">
-        <v>95154793</v>
+        <v>10135387</v>
       </c>
       <c r="L3" t="n">
-        <v>109502969</v>
+        <v>11616604</v>
       </c>
       <c r="M3" t="n">
-        <v>135907121</v>
+        <v>14925414</v>
       </c>
       <c r="N3" t="n">
-        <v>145649922</v>
+        <v>16176788</v>
       </c>
       <c r="O3" t="n">
-        <v>141000535</v>
+        <v>15577179</v>
       </c>
       <c r="P3" t="n">
-        <v>144973697</v>
+        <v>16082165</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8783740401268005</v>
+        <v>0.7911561131477356</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7318718433380127</v>
+        <v>0.5659916996955872</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6074602603912354</v>
+        <v>0.4246025383472443</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1895674765110016</v>
+        <v>0.1075509786605835</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6777514815330505</v>
+        <v>0.5021344423294067</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6339165568351746</v>
+        <v>0.4926530718803406</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>43199395</v>
+        <v>4763805</v>
       </c>
       <c r="Z3" t="n">
-        <v>1777968</v>
+        <v>196543</v>
       </c>
       <c r="AA3" t="n">
-        <v>76428</v>
+        <v>8427</v>
       </c>
       <c r="AB3" t="n">
-        <v>61298</v>
+        <v>6839</v>
       </c>
       <c r="AC3" t="n">
-        <v>269</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>270</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>90149598</v>
+        <v>10016622</v>
       </c>
       <c r="AF3" t="n">
-        <v>99866284</v>
+        <v>11129066</v>
       </c>
       <c r="AG3" t="n">
-        <v>114872156</v>
+        <v>12733718</v>
       </c>
       <c r="AH3" t="n">
-        <v>137364636</v>
+        <v>15256890</v>
       </c>
       <c r="AI3" t="n">
-        <v>145891115</v>
+        <v>16209518</v>
       </c>
       <c r="AJ3" t="n">
-        <v>141928554</v>
+        <v>15768153</v>
       </c>
       <c r="AK3" t="n">
-        <v>145106283</v>
+        <v>16122647</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9575262069702148</v>
+        <v>0.95742267370224</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.909828245639801</v>
+        <v>0.9092735648155212</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8573063611984253</v>
+        <v>0.8566092252731323</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6612093448638916</v>
+        <v>0.6602116227149963</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9014564752578735</v>
+        <v>0.9011421799659729</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9312204718589783</v>
+        <v>0.931006908416748</v>
       </c>
     </row>
     <row r="4">
@@ -929,127 +929,127 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>6241722</v>
+        <v>1118259</v>
       </c>
       <c r="E4" t="n">
-        <v>21583038</v>
+        <v>1871352</v>
       </c>
       <c r="F4" t="n">
-        <v>1429404</v>
+        <v>252539</v>
       </c>
       <c r="G4" t="n">
-        <v>56622</v>
+        <v>13358</v>
       </c>
       <c r="H4" t="n">
-        <v>164268</v>
+        <v>45707</v>
       </c>
       <c r="I4" t="n">
-        <v>15134</v>
+        <v>5109</v>
       </c>
       <c r="J4" t="n">
-        <v>3465</v>
+        <v>385</v>
       </c>
       <c r="K4" t="n">
-        <v>6695979</v>
+        <v>1218558</v>
       </c>
       <c r="L4" t="n">
-        <v>7973243</v>
+        <v>1406672</v>
       </c>
       <c r="M4" t="n">
-        <v>2648582</v>
+        <v>464307</v>
       </c>
       <c r="N4" t="n">
-        <v>512722</v>
+        <v>63115</v>
       </c>
       <c r="O4" t="n">
-        <v>1377344</v>
+        <v>241040</v>
       </c>
       <c r="P4" t="n">
-        <v>251895</v>
+        <v>53749</v>
       </c>
       <c r="Q4" t="n">
         <v>0.9999695420265198</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8667628169059753</v>
+        <v>0.777144193649292</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7310526371002197</v>
+        <v>0.56842440366745</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6319921016693115</v>
+        <v>0.4426148235797882</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2074638307094574</v>
+        <v>0.1187622770667076</v>
       </c>
       <c r="V4" t="n">
-        <v>0.685316264629364</v>
+        <v>0.5088807344436646</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7128197550773621</v>
+        <v>0.5566202402114868</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1853220</v>
+        <v>210159</v>
       </c>
       <c r="Z4" t="n">
-        <v>26831006</v>
+        <v>3006353</v>
       </c>
       <c r="AA4" t="n">
-        <v>745446</v>
+        <v>83023</v>
       </c>
       <c r="AB4" t="n">
-        <v>49654</v>
+        <v>5590</v>
       </c>
       <c r="AC4" t="n">
-        <v>10250</v>
+        <v>1131</v>
       </c>
       <c r="AD4" t="n">
-        <v>612</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1984488</v>
+        <v>224879</v>
       </c>
       <c r="AG4" t="n">
-        <v>2604056</v>
+        <v>289558</v>
       </c>
       <c r="AH4" t="n">
-        <v>1191067</v>
+        <v>132831</v>
       </c>
       <c r="AI4" t="n">
-        <v>271529</v>
+        <v>30385</v>
       </c>
       <c r="AJ4" t="n">
-        <v>449325</v>
+        <v>50066</v>
       </c>
       <c r="AK4" t="n">
-        <v>119309</v>
+        <v>13267</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9568024277687073</v>
+        <v>0.9561707377433777</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106794595718384</v>
+        <v>0.9107076525688171</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8577696084976196</v>
+        <v>0.8574937582015991</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6615287065505981</v>
+        <v>0.660554051399231</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9017359018325806</v>
+        <v>0.9015724062919617</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.931333601474762</v>
+        <v>0.9312376976013184</v>
       </c>
     </row>
     <row r="5">
@@ -1059,152 +1059,152 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>314188</v>
+        <v>74015</v>
       </c>
       <c r="E5" t="n">
-        <v>2217603</v>
+        <v>327282</v>
       </c>
       <c r="F5" t="n">
-        <v>5109164</v>
+        <v>399075</v>
       </c>
       <c r="G5" t="n">
-        <v>154953</v>
+        <v>21080</v>
       </c>
       <c r="H5" t="n">
-        <v>561263</v>
+        <v>104606</v>
       </c>
       <c r="I5" t="n">
-        <v>53526</v>
+        <v>13821</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>5487232</v>
+        <v>1039135</v>
       </c>
       <c r="L5" t="n">
-        <v>7907150</v>
+        <v>1434972</v>
       </c>
       <c r="M5" t="n">
-        <v>3301533</v>
+        <v>540804</v>
       </c>
       <c r="N5" t="n">
-        <v>651390</v>
+        <v>80050</v>
       </c>
       <c r="O5" t="n">
-        <v>1478644</v>
+        <v>254599</v>
       </c>
       <c r="P5" t="n">
-        <v>637281</v>
+        <v>98266</v>
       </c>
       <c r="Q5" t="n">
         <v>0.9999763965606689</v>
       </c>
       <c r="R5" t="n">
-        <v>0.917102038860321</v>
+        <v>0.8617423176765442</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8919454216957092</v>
+        <v>0.8259820342063904</v>
       </c>
       <c r="T5" t="n">
-        <v>0.959513783454895</v>
+        <v>0.9384485483169556</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9920790791511536</v>
+        <v>0.9912328124046326</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9805670976638794</v>
+        <v>0.9696478247642517</v>
       </c>
       <c r="W5" t="n">
-        <v>0.993949830532074</v>
+        <v>0.9906908273696899</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>72334</v>
+        <v>8098</v>
       </c>
       <c r="Z5" t="n">
-        <v>769884</v>
+        <v>86770</v>
       </c>
       <c r="AA5" t="n">
-        <v>7210544</v>
+        <v>805109</v>
       </c>
       <c r="AB5" t="n">
-        <v>89719</v>
+        <v>10018</v>
       </c>
       <c r="AC5" t="n">
-        <v>262519</v>
+        <v>29251</v>
       </c>
       <c r="AD5" t="n">
-        <v>5697</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1916233</v>
+        <v>211850</v>
       </c>
       <c r="AG5" t="n">
-        <v>2659182</v>
+        <v>299971</v>
       </c>
       <c r="AH5" t="n">
-        <v>1200153</v>
+        <v>134770</v>
       </c>
       <c r="AI5" t="n">
-        <v>272305</v>
+        <v>30478</v>
       </c>
       <c r="AJ5" t="n">
-        <v>452169</v>
+        <v>50554</v>
       </c>
       <c r="AK5" t="n">
-        <v>119732</v>
+        <v>13363</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9734584093093872</v>
+        <v>0.9732553958892822</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9641875028610229</v>
+        <v>0.9638981223106384</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9837294816970825</v>
+        <v>0.9836125373840332</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9962996244430542</v>
+        <v>0.99627286195755</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.993865966796875</v>
+        <v>0.9938381910324097</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983735084533691</v>
+        <v>0.9983692169189453</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>187</v>
+        <v>21</v>
       </c>
       <c r="D6" t="n">
-        <v>121272</v>
+        <v>17923</v>
       </c>
       <c r="E6" t="n">
-        <v>184389</v>
+        <v>23665</v>
       </c>
       <c r="F6" t="n">
-        <v>248790</v>
+        <v>24483</v>
       </c>
       <c r="G6" t="n">
-        <v>152366</v>
+        <v>9647</v>
       </c>
       <c r="H6" t="n">
-        <v>89709</v>
+        <v>12304</v>
       </c>
       <c r="I6" t="n">
-        <v>7043</v>
+        <v>1654</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>58491</v>
+        <v>6586</v>
       </c>
       <c r="Z6" t="n">
-        <v>48185</v>
+        <v>5354</v>
       </c>
       <c r="AA6" t="n">
-        <v>98390</v>
+        <v>11038</v>
       </c>
       <c r="AB6" t="n">
-        <v>531451</v>
+        <v>59219</v>
       </c>
       <c r="AC6" t="n">
-        <v>62910</v>
+        <v>7019</v>
       </c>
       <c r="AD6" t="n">
-        <v>4329</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1263,22 +1263,22 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>18089</v>
+        <v>8119</v>
       </c>
       <c r="E7" t="n">
-        <v>238551</v>
+        <v>63829</v>
       </c>
       <c r="F7" t="n">
-        <v>771303</v>
+        <v>127110</v>
       </c>
       <c r="G7" t="n">
-        <v>275024</v>
+        <v>22665</v>
       </c>
       <c r="H7" t="n">
-        <v>3109877</v>
+        <v>256782</v>
       </c>
       <c r="I7" t="n">
-        <v>175677</v>
+        <v>32876</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>191</v>
+        <v>8</v>
       </c>
       <c r="Z7" t="n">
-        <v>7290</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>267822</v>
+        <v>30010</v>
       </c>
       <c r="AB7" t="n">
-        <v>68465</v>
+        <v>7671</v>
       </c>
       <c r="AC7" t="n">
-        <v>4136352</v>
+        <v>460827</v>
       </c>
       <c r="AD7" t="n">
-        <v>108401</v>
+        <v>12055</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>708</v>
+        <v>242</v>
       </c>
       <c r="E8" t="n">
-        <v>20203</v>
+        <v>7002</v>
       </c>
       <c r="F8" t="n">
-        <v>49954</v>
+        <v>13879</v>
       </c>
       <c r="G8" t="n">
-        <v>16174</v>
+        <v>3192</v>
       </c>
       <c r="H8" t="n">
-        <v>550223</v>
+        <v>73950</v>
       </c>
       <c r="I8" t="n">
-        <v>1103527</v>
+        <v>95420</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>252</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>729</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>2981</v>
+        <v>333</v>
       </c>
       <c r="AB8" t="n">
-        <v>2393</v>
+        <v>267</v>
       </c>
       <c r="AC8" t="n">
-        <v>113377</v>
+        <v>12654</v>
       </c>
       <c r="AD8" t="n">
-        <v>1621076</v>
+        <v>180323</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
